--- a/SET-Scan/listedCompanies_en_US.xlsx
+++ b/SET-Scan/listedCompanies_en_US.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joeki\Downloads\SET_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4184D5B1-AA70-46CA-B112-19B8C9894A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2631FC1B-03A9-45BE-BF66-2DE3FB4E2456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{0FFCD533-2399-4E58-9523-34A2BA27D5BB}"/>
   </bookViews>
@@ -16507,7 +16507,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -16523,6 +16523,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -43952,7 +43955,7 @@
       </c>
     </row>
     <row r="847" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A847" t="b">
+      <c r="A847" s="6" t="b">
         <v>1</v>
       </c>
       <c r="B847" t="s">
